--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_36.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1457238.967751149</v>
+        <v>1461738.660558725</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5413711.842050619</v>
+        <v>5302419.152462203</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11225139.03465134</v>
+        <v>11232339.78768198</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6521010.702311692</v>
+        <v>6536501.62133356</v>
       </c>
     </row>
     <row r="11">
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2128,16 +2128,16 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
     </row>
     <row r="21">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2283,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
     </row>
     <row r="25">
@@ -2517,19 +2517,19 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2551,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2675,13 +2675,13 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -2748,22 +2748,22 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2864,13 +2864,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.7526328886747309</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2909,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2985,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3028,13 +3028,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3152,16 +3152,16 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.7526328886747309</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3237,10 +3237,10 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3307,16 +3307,16 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.7526328886747309</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
     </row>
     <row r="37">
@@ -3411,19 +3411,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.9360648988932353</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
     </row>
     <row r="39">
@@ -3572,16 +3572,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.7526328886747327</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
     </row>
     <row r="40">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3711,13 +3711,13 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
     </row>
     <row r="41">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3787,13 +3787,13 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3869,13 +3869,13 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
     </row>
     <row r="43">
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>8.478328118847974</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>18.11144729538444</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>8.929179130375823</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>28.01967470280152</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>18.29673215419101</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>8.573789605580503</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>9.914484516818138</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>19.4439405087113</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>28.97339650060446</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>29.93888469568149</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>20.21594214707098</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>10.49299959846046</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>19.0569673952766</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>9.33402484666609</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.7700570498499525</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>10.29951304174311</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>19.82896903363628</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>29.35842502552944</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>38.50285249249762</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>28.77990994388711</v>
       </c>
     </row>
     <row r="44">
@@ -9387,16 +9387,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M20" t="n">
-        <v>230.3462332272727</v>
+        <v>239.5830286484527</v>
       </c>
       <c r="N20" t="n">
-        <v>229.4130635965909</v>
+        <v>239.0387767197153</v>
       </c>
       <c r="O20" t="n">
-        <v>230.0982114216867</v>
+        <v>239.7239245448111</v>
       </c>
       <c r="P20" t="n">
-        <v>231.2329957552695</v>
+        <v>240.8587088783939</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,16 +9460,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>147.078234395539</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>151.7597470451427</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>140.9674252064577</v>
       </c>
       <c r="O21" t="n">
         <v>142.5962444444444</v>
@@ -9478,7 +9478,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>149.6074872091459</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9542,16 +9542,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>134.8846762812383</v>
+        <v>144.5103894043627</v>
       </c>
       <c r="M22" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N22" t="n">
-        <v>127.6855444652332</v>
+        <v>136.9223398864132</v>
       </c>
       <c r="O22" t="n">
-        <v>138.4565384518428</v>
+        <v>148.0822515749672</v>
       </c>
       <c r="P22" t="n">
         <v>135.0065633140411</v>
@@ -9624,16 +9624,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
-        <v>230.3462332272727</v>
+        <v>239.5830286484527</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>239.0387767197153</v>
       </c>
       <c r="O23" t="n">
-        <v>230.0982114216867</v>
+        <v>239.7239245448111</v>
       </c>
       <c r="P23" t="n">
-        <v>231.2329957552695</v>
+        <v>240.8587088783939</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9700,16 +9700,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>147.7911752010542</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>151.7597470451427</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>140.9674252064577</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444444</v>
+        <v>152.2219575675688</v>
       </c>
       <c r="P24" t="n">
         <v>133.9744074143302</v>
@@ -9779,16 +9779,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>134.8846762812383</v>
+        <v>144.5103894043627</v>
       </c>
       <c r="M25" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N25" t="n">
-        <v>127.6855444652332</v>
+        <v>136.9223398864132</v>
       </c>
       <c r="O25" t="n">
-        <v>138.4565384518428</v>
+        <v>148.0822515749672</v>
       </c>
       <c r="P25" t="n">
         <v>135.0065633140411</v>
@@ -9858,16 +9858,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L26" t="n">
-        <v>235.7664149699872</v>
+        <v>245.3921280931116</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272727</v>
+        <v>239.9719463503971</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>239.0387767197153</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>239.3350068428667</v>
       </c>
       <c r="P26" t="n">
         <v>231.2329957552695</v>
@@ -9940,16 +9940,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>151.7597470451427</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>140.9674252064577</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>151.8330398656244</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>143.6001205374546</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10016,16 +10016,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>134.8846762812383</v>
+        <v>144.5103894043627</v>
       </c>
       <c r="M28" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N28" t="n">
-        <v>127.6855444652332</v>
+        <v>137.3112575883576</v>
       </c>
       <c r="O28" t="n">
-        <v>138.4565384518428</v>
+        <v>147.6933338730228</v>
       </c>
       <c r="P28" t="n">
         <v>135.0065633140411</v>
@@ -10092,16 +10092,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>229.7155641681049</v>
       </c>
       <c r="L29" t="n">
-        <v>235.7664149699872</v>
+        <v>245.3921280931116</v>
       </c>
       <c r="M29" t="n">
-        <v>230.3462332272727</v>
+        <v>239.9719463503971</v>
       </c>
       <c r="N29" t="n">
-        <v>229.4130635965909</v>
+        <v>238.6498590177709</v>
       </c>
       <c r="O29" t="n">
         <v>230.0982114216867</v>
@@ -10171,7 +10171,7 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>147.078234395539</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
@@ -10183,13 +10183,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>152.2219575675688</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>143.6001205374546</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>149.6074872091459</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,16 +10253,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>134.8846762812383</v>
+        <v>144.1214717024183</v>
       </c>
       <c r="M31" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>137.3112575883576</v>
       </c>
       <c r="O31" t="n">
-        <v>138.4565384518428</v>
+        <v>148.0822515749672</v>
       </c>
       <c r="P31" t="n">
         <v>135.0065633140411</v>
@@ -10332,16 +10332,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>235.7664149699872</v>
+        <v>245.0032103911672</v>
       </c>
       <c r="M32" t="n">
-        <v>230.3462332272727</v>
+        <v>239.9719463503971</v>
       </c>
       <c r="N32" t="n">
-        <v>229.4130635965909</v>
+        <v>239.0387767197153</v>
       </c>
       <c r="O32" t="n">
-        <v>230.0982114216867</v>
+        <v>239.7239245448111</v>
       </c>
       <c r="P32" t="n">
         <v>231.2329957552695</v>
@@ -10408,16 +10408,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>147.4671520974834</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>148.1800929029986</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>151.7597470451427</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>140.5785075045133</v>
       </c>
       <c r="O33" t="n">
         <v>142.5962444444444</v>
@@ -10490,16 +10490,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>134.8846762812383</v>
+        <v>144.5103894043627</v>
       </c>
       <c r="M34" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N34" t="n">
-        <v>127.6855444652332</v>
+        <v>137.3112575883576</v>
       </c>
       <c r="O34" t="n">
-        <v>138.4565384518428</v>
+        <v>147.6933338730228</v>
       </c>
       <c r="P34" t="n">
         <v>135.0065633140411</v>
@@ -10566,19 +10566,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>220.0898510449805</v>
+        <v>229.3266464661605</v>
       </c>
       <c r="L35" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272727</v>
+        <v>239.9719463503971</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>239.0387767197153</v>
       </c>
       <c r="O35" t="n">
-        <v>230.0982114216867</v>
+        <v>239.7239245448111</v>
       </c>
       <c r="P35" t="n">
         <v>231.2329957552695</v>
@@ -10654,16 +10654,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>140.5785075045133</v>
       </c>
       <c r="O36" t="n">
-        <v>142.5962444444444</v>
+        <v>152.2219575675688</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>143.6001205374546</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>149.6074872091459</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10727,16 +10727,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>134.8846762812383</v>
+        <v>144.1214717024183</v>
       </c>
       <c r="M37" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N37" t="n">
-        <v>127.6855444652332</v>
+        <v>137.3112575883576</v>
       </c>
       <c r="O37" t="n">
-        <v>138.4565384518428</v>
+        <v>148.0822515749672</v>
       </c>
       <c r="P37" t="n">
         <v>135.0065633140411</v>
@@ -10803,16 +10803,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>220.0898510449805</v>
+        <v>229.7155641681049</v>
       </c>
       <c r="L38" t="n">
-        <v>235.7664149699872</v>
+        <v>245.3921280931116</v>
       </c>
       <c r="M38" t="n">
-        <v>230.3462332272727</v>
+        <v>239.9719463503971</v>
       </c>
       <c r="N38" t="n">
-        <v>229.4130635965909</v>
+        <v>238.6498590177709</v>
       </c>
       <c r="O38" t="n">
         <v>230.0982114216867</v>
@@ -10891,16 +10891,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>140.9674252064577</v>
       </c>
       <c r="O39" t="n">
-        <v>142.5962444444444</v>
+        <v>152.2219575675688</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>143.6001205374546</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>149.2185695072015</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10964,16 +10964,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>134.8846762812383</v>
+        <v>144.1214717024183</v>
       </c>
       <c r="M40" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N40" t="n">
-        <v>127.6855444652332</v>
+        <v>137.3112575883576</v>
       </c>
       <c r="O40" t="n">
-        <v>138.4565384518428</v>
+        <v>148.0822515749672</v>
       </c>
       <c r="P40" t="n">
         <v>135.0065633140411</v>
@@ -11046,16 +11046,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272727</v>
+        <v>239.5830286484527</v>
       </c>
       <c r="N41" t="n">
-        <v>229.4130635965909</v>
+        <v>239.0387767197153</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>239.7239245448111</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>240.8587088783939</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,22 +11119,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>147.4671520974834</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>148.1800929029986</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833333</v>
+        <v>140.9674252064577</v>
       </c>
       <c r="O42" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>143.2112028355102</v>
       </c>
       <c r="Q42" t="n">
         <v>139.9817740860215</v>
@@ -11201,16 +11201,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>134.8846762812383</v>
+        <v>144.5103894043627</v>
       </c>
       <c r="M43" t="n">
-        <v>138.9257839476051</v>
+        <v>148.5514970707295</v>
       </c>
       <c r="N43" t="n">
-        <v>127.6855444652332</v>
+        <v>137.3112575883576</v>
       </c>
       <c r="O43" t="n">
-        <v>138.4565384518428</v>
+        <v>147.6933338730228</v>
       </c>
       <c r="P43" t="n">
         <v>135.0065633140411</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>369.7338416634806</v>
+        <v>370.7845523088681</v>
       </c>
       <c r="C11" t="n">
-        <v>352.2728917710076</v>
+        <v>353.323602416395</v>
       </c>
       <c r="D11" t="n">
-        <v>341.683041620683</v>
+        <v>342.7337522660704</v>
       </c>
       <c r="E11" t="n">
-        <v>368.9303700722618</v>
+        <v>369.9810807176493</v>
       </c>
       <c r="F11" t="n">
-        <v>393.8760457417114</v>
+        <v>394.9267563870989</v>
       </c>
       <c r="G11" t="n">
-        <v>402.302737515135</v>
+        <v>403.3534481605225</v>
       </c>
       <c r="H11" t="n">
-        <v>326.4748021157671</v>
+        <v>327.5255127611546</v>
       </c>
       <c r="I11" t="n">
-        <v>197.4758895704059</v>
+        <v>198.5266002157934</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>136.8691179411497</v>
+        <v>137.9198285865372</v>
       </c>
       <c r="S11" t="n">
-        <v>196.0200695862453</v>
+        <v>197.0707802316328</v>
       </c>
       <c r="T11" t="n">
-        <v>210.0958495641314</v>
+        <v>211.1465602095188</v>
       </c>
       <c r="U11" t="n">
-        <v>238.3456529078365</v>
+        <v>239.396363553224</v>
       </c>
       <c r="V11" t="n">
-        <v>314.7522584701349</v>
+        <v>315.8029691155224</v>
       </c>
       <c r="W11" t="n">
-        <v>336.240968717413</v>
+        <v>337.2916793628005</v>
       </c>
       <c r="X11" t="n">
-        <v>356.731100678469</v>
+        <v>357.7818113238565</v>
       </c>
       <c r="Y11" t="n">
-        <v>373.2379386560536</v>
+        <v>374.2886493014411</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153.5331836498673</v>
+        <v>154.5838942952548</v>
       </c>
       <c r="C12" t="n">
-        <v>159.7084989883157</v>
+        <v>160.7592096337032</v>
       </c>
       <c r="D12" t="n">
-        <v>134.4450655646388</v>
+        <v>135.4957762100262</v>
       </c>
       <c r="E12" t="n">
-        <v>144.6450804554009</v>
+        <v>145.6957911007884</v>
       </c>
       <c r="F12" t="n">
-        <v>132.0692123933839</v>
+        <v>133.1199230387714</v>
       </c>
       <c r="G12" t="n">
-        <v>124.3435171632106</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H12" t="n">
-        <v>99.23544423649646</v>
+        <v>100.2861548818839</v>
       </c>
       <c r="I12" t="n">
-        <v>76.39663285141508</v>
+        <v>77.44734349680256</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>87.15783415264313</v>
+        <v>88.20854479803062</v>
       </c>
       <c r="S12" t="n">
-        <v>158.6831711038378</v>
+        <v>159.7338817492253</v>
       </c>
       <c r="T12" t="n">
-        <v>187.1647286948216</v>
+        <v>188.2154393402091</v>
       </c>
       <c r="U12" t="n">
-        <v>212.9413820809748</v>
+        <v>213.9920927263623</v>
       </c>
       <c r="V12" t="n">
-        <v>219.8005871494253</v>
+        <v>220.8512977948128</v>
       </c>
       <c r="W12" t="n">
-        <v>238.6949831609196</v>
+        <v>239.7456938063071</v>
       </c>
       <c r="X12" t="n">
-        <v>192.7729852034775</v>
+        <v>193.823695848865</v>
       </c>
       <c r="Y12" t="n">
-        <v>192.6826957773044</v>
+        <v>193.7334064226918</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>166.8319801819373</v>
+        <v>167.8826908273248</v>
       </c>
       <c r="C13" t="n">
-        <v>154.2468210986278</v>
+        <v>155.2975317440153</v>
       </c>
       <c r="D13" t="n">
-        <v>135.6154730182124</v>
+        <v>136.6661836635998</v>
       </c>
       <c r="E13" t="n">
-        <v>133.4339626465692</v>
+        <v>134.4846732919567</v>
       </c>
       <c r="F13" t="n">
-        <v>132.4210480229312</v>
+        <v>133.4717586683187</v>
       </c>
       <c r="G13" t="n">
-        <v>154.9909793584588</v>
+        <v>156.0416900038462</v>
       </c>
       <c r="H13" t="n">
-        <v>149.2271725074396</v>
+        <v>150.2778831528271</v>
       </c>
       <c r="I13" t="n">
-        <v>142.4504749272583</v>
+        <v>143.5011855726458</v>
       </c>
       <c r="J13" t="n">
-        <v>80.35918011667277</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="K13" t="n">
-        <v>9.269491825882852</v>
+        <v>10.32020247127033</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>73.16204325169439</v>
+        <v>74.21275389708187</v>
       </c>
       <c r="R13" t="n">
-        <v>164.2933913771695</v>
+        <v>165.344102022557</v>
       </c>
       <c r="S13" t="n">
-        <v>211.0165980369723</v>
+        <v>212.0673086823597</v>
       </c>
       <c r="T13" t="n">
-        <v>214.9455894282815</v>
+        <v>215.996300073669</v>
       </c>
       <c r="U13" t="n">
-        <v>273.3190293564909</v>
+        <v>274.3697400018784</v>
       </c>
       <c r="V13" t="n">
-        <v>239.137643323828</v>
+        <v>240.1883539692155</v>
       </c>
       <c r="W13" t="n">
-        <v>273.522998336591</v>
+        <v>274.5737089819785</v>
       </c>
       <c r="X13" t="n">
-        <v>212.7096553890372</v>
+        <v>213.7603660344246</v>
       </c>
       <c r="Y13" t="n">
-        <v>205.5846533520948</v>
+        <v>206.6353639974823</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>56.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,31 +23610,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3591801166727748</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>56.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,31 +23847,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3591801166727748</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>159.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>289.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>313.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>56.86911794114968</v>
+        <v>46.8842247013525</v>
       </c>
       <c r="S20" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>234.7522584701349</v>
+        <v>224.7673652303377</v>
       </c>
       <c r="W20" t="n">
-        <v>256.240968717413</v>
+        <v>247.4034604818923</v>
       </c>
       <c r="X20" t="n">
-        <v>276.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>293.2379386560536</v>
+        <v>283.2530454162564</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>73.53318364986734</v>
+        <v>63.54829041007016</v>
       </c>
       <c r="C21" t="n">
-        <v>79.70849898831574</v>
+        <v>69.72360574851857</v>
       </c>
       <c r="D21" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>64.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>52.06921239338388</v>
+        <v>43.23170415786313</v>
       </c>
       <c r="G21" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>78.68317110383782</v>
+        <v>68.69827786404065</v>
       </c>
       <c r="T21" t="n">
-        <v>107.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>112.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,31 +24084,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>69.22717250743958</v>
+        <v>59.2422792676424</v>
       </c>
       <c r="I22" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3591801166727748</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>84.29339137716948</v>
+        <v>74.30849813737231</v>
       </c>
       <c r="S22" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>134.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>193.3190293564909</v>
+        <v>183.3341361166937</v>
       </c>
       <c r="V22" t="n">
-        <v>159.137643323828</v>
+        <v>150.3001350883073</v>
       </c>
       <c r="W22" t="n">
-        <v>193.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>132.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>289.7338416634806</v>
+        <v>280.8963334279599</v>
       </c>
       <c r="C23" t="n">
-        <v>272.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>261.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>288.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>313.8760457417114</v>
+        <v>303.8911525019143</v>
       </c>
       <c r="G23" t="n">
-        <v>322.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>246.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>117.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>56.86911794114968</v>
+        <v>46.8842247013525</v>
       </c>
       <c r="S23" t="n">
-        <v>116.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>130.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>158.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>234.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>256.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>276.731100678469</v>
+        <v>266.7462074386719</v>
       </c>
       <c r="Y23" t="n">
-        <v>293.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>73.53318364986734</v>
+        <v>63.54829041007016</v>
       </c>
       <c r="C24" t="n">
-        <v>79.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>54.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>64.64508045540094</v>
+        <v>54.66018721560376</v>
       </c>
       <c r="F24" t="n">
-        <v>52.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>44.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>19.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>7.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>78.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>107.1647286948216</v>
+        <v>98.32722045930086</v>
       </c>
       <c r="U24" t="n">
-        <v>132.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>139.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>158.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>112.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>112.6826957773044</v>
+        <v>102.6978025375072</v>
       </c>
     </row>
     <row r="25">
@@ -24321,31 +24321,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>86.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>74.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>55.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>53.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>52.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>74.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>69.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>62.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3591801166710553</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>84.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>131.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>134.9455894282815</v>
+        <v>124.9606961884843</v>
       </c>
       <c r="U25" t="n">
-        <v>193.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>159.137643323828</v>
+        <v>149.1527500840308</v>
       </c>
       <c r="W25" t="n">
-        <v>193.522998336591</v>
+        <v>183.5381050967938</v>
       </c>
       <c r="X25" t="n">
-        <v>132.7096553890372</v>
+        <v>123.8721471535164</v>
       </c>
       <c r="Y25" t="n">
-        <v>125.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>294.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>277.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>266.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>293.9303700722618</v>
+        <v>282.9080240977223</v>
       </c>
       <c r="F26" t="n">
-        <v>318.8760457417114</v>
+        <v>307.853699767172</v>
       </c>
       <c r="G26" t="n">
-        <v>327.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>251.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>122.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>61.86911794114968</v>
+        <v>50.8467719666102</v>
       </c>
       <c r="S26" t="n">
-        <v>121.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>135.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>163.3456529078365</v>
+        <v>153.4706919375735</v>
       </c>
       <c r="V26" t="n">
-        <v>239.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>261.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>281.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>298.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>84.70849898831574</v>
+        <v>74.83353801805269</v>
       </c>
       <c r="D27" t="n">
-        <v>59.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>69.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>57.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>49.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>24.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
-        <v>1.396632851415077</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>12.15783415264313</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>83.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>112.1647286948216</v>
+        <v>101.1423827202821</v>
       </c>
       <c r="U27" t="n">
-        <v>137.9413820809748</v>
+        <v>126.9190361064353</v>
       </c>
       <c r="V27" t="n">
-        <v>144.8005871494253</v>
+        <v>133.7782411748858</v>
       </c>
       <c r="W27" t="n">
-        <v>163.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>117.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>117.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>91.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>79.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>60.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>58.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>57.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>79.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>74.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>67.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>5.359180116672775</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>89.29339137716948</v>
+        <v>78.27104540262999</v>
       </c>
       <c r="S28" t="n">
-        <v>136.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>139.9455894282815</v>
+        <v>128.923243453742</v>
       </c>
       <c r="U28" t="n">
-        <v>198.3190293564909</v>
+        <v>188.4440683862279</v>
       </c>
       <c r="V28" t="n">
-        <v>164.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>198.522998336591</v>
+        <v>187.5006523620515</v>
       </c>
       <c r="X28" t="n">
-        <v>137.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>130.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>240.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C29" t="n">
-        <v>223.2728917710076</v>
+        <v>218.3036614846725</v>
       </c>
       <c r="D29" t="n">
-        <v>212.683041620683</v>
+        <v>207.7138113343479</v>
       </c>
       <c r="E29" t="n">
-        <v>239.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F29" t="n">
-        <v>264.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G29" t="n">
-        <v>273.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H29" t="n">
-        <v>197.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I29" t="n">
-        <v>68.47588957040591</v>
+        <v>63.50665928407087</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>7.869117941149682</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S29" t="n">
-        <v>67.02006958624534</v>
+        <v>63.19822430418673</v>
       </c>
       <c r="T29" t="n">
-        <v>81.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U29" t="n">
-        <v>109.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V29" t="n">
-        <v>185.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W29" t="n">
-        <v>207.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X29" t="n">
-        <v>227.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y29" t="n">
-        <v>244.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="30">
@@ -24716,19 +24716,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C30" t="n">
-        <v>30.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D30" t="n">
-        <v>5.445065564638753</v>
+        <v>9.348915512753388</v>
       </c>
       <c r="E30" t="n">
-        <v>15.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F30" t="n">
-        <v>3.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>29.68317110383782</v>
+        <v>24.71394081750278</v>
       </c>
       <c r="T30" t="n">
-        <v>58.1647286948216</v>
+        <v>53.19549840848656</v>
       </c>
       <c r="U30" t="n">
-        <v>83.94138208097482</v>
+        <v>78.97215179463979</v>
       </c>
       <c r="V30" t="n">
-        <v>90.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W30" t="n">
-        <v>109.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X30" t="n">
-        <v>63.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y30" t="n">
-        <v>63.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C31" t="n">
-        <v>25.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D31" t="n">
-        <v>6.615473018212356</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E31" t="n">
-        <v>4.433962646569171</v>
+        <v>0.6121173645105618</v>
       </c>
       <c r="F31" t="n">
-        <v>3.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G31" t="n">
-        <v>25.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H31" t="n">
-        <v>20.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I31" t="n">
-        <v>13.45047492725828</v>
+        <v>8.481244640923244</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>35.29339137716948</v>
+        <v>30.32416109083444</v>
       </c>
       <c r="S31" t="n">
-        <v>82.01659803697225</v>
+        <v>77.04736775063722</v>
       </c>
       <c r="T31" t="n">
-        <v>85.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U31" t="n">
-        <v>144.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V31" t="n">
-        <v>110.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W31" t="n">
-        <v>144.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X31" t="n">
-        <v>83.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y31" t="n">
-        <v>76.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>240.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C32" t="n">
-        <v>223.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D32" t="n">
-        <v>212.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E32" t="n">
-        <v>239.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F32" t="n">
-        <v>264.8760457417114</v>
+        <v>259.9068154553764</v>
       </c>
       <c r="G32" t="n">
-        <v>273.302737515135</v>
+        <v>268.3335072288</v>
       </c>
       <c r="H32" t="n">
-        <v>197.4748021157671</v>
+        <v>193.6529568337085</v>
       </c>
       <c r="I32" t="n">
-        <v>68.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7.869117941149682</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S32" t="n">
-        <v>67.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T32" t="n">
-        <v>81.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U32" t="n">
-        <v>109.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V32" t="n">
-        <v>185.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W32" t="n">
-        <v>207.240968717413</v>
+        <v>202.271738431078</v>
       </c>
       <c r="X32" t="n">
-        <v>227.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y32" t="n">
-        <v>244.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="33">
@@ -24953,19 +24953,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C33" t="n">
-        <v>30.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D33" t="n">
-        <v>5.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E33" t="n">
-        <v>15.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F33" t="n">
-        <v>3.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>29.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T33" t="n">
-        <v>58.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U33" t="n">
-        <v>83.94138208097482</v>
+        <v>78.97215179463979</v>
       </c>
       <c r="V33" t="n">
-        <v>90.80058714942527</v>
+        <v>85.83135686309024</v>
       </c>
       <c r="W33" t="n">
-        <v>109.6949831609196</v>
+        <v>104.7257528745846</v>
       </c>
       <c r="X33" t="n">
-        <v>63.77298520347748</v>
+        <v>67.67683515159212</v>
       </c>
       <c r="Y33" t="n">
-        <v>63.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>37.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C34" t="n">
-        <v>25.24682109862783</v>
+        <v>21.42497581656922</v>
       </c>
       <c r="D34" t="n">
-        <v>6.615473018212356</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E34" t="n">
-        <v>4.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F34" t="n">
-        <v>3.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G34" t="n">
-        <v>25.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H34" t="n">
-        <v>20.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I34" t="n">
-        <v>13.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>35.29339137716948</v>
+        <v>30.32416109083444</v>
       </c>
       <c r="S34" t="n">
-        <v>82.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T34" t="n">
-        <v>85.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U34" t="n">
-        <v>144.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V34" t="n">
-        <v>110.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W34" t="n">
-        <v>144.522998336591</v>
+        <v>139.553768050256</v>
       </c>
       <c r="X34" t="n">
-        <v>83.70965538903715</v>
+        <v>78.74042510270212</v>
       </c>
       <c r="Y34" t="n">
-        <v>76.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>240.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C35" t="n">
-        <v>223.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D35" t="n">
-        <v>212.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E35" t="n">
-        <v>239.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F35" t="n">
-        <v>264.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G35" t="n">
-        <v>273.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H35" t="n">
-        <v>197.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I35" t="n">
-        <v>68.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>7.869117941149682</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S35" t="n">
-        <v>67.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T35" t="n">
-        <v>81.09584956413136</v>
+        <v>76.12661927779632</v>
       </c>
       <c r="U35" t="n">
-        <v>109.3456529078365</v>
+        <v>105.5238076257779</v>
       </c>
       <c r="V35" t="n">
-        <v>185.7522584701349</v>
+        <v>180.7830281837999</v>
       </c>
       <c r="W35" t="n">
-        <v>207.240968717413</v>
+        <v>202.271738431078</v>
       </c>
       <c r="X35" t="n">
-        <v>227.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y35" t="n">
-        <v>244.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24.53318364986734</v>
+        <v>19.5639533635323</v>
       </c>
       <c r="C36" t="n">
-        <v>30.70849898831574</v>
+        <v>34.61234893643037</v>
       </c>
       <c r="D36" t="n">
-        <v>5.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E36" t="n">
-        <v>15.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F36" t="n">
-        <v>3.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>29.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T36" t="n">
-        <v>58.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U36" t="n">
-        <v>83.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V36" t="n">
-        <v>90.80058714942527</v>
+        <v>85.83135686309024</v>
       </c>
       <c r="W36" t="n">
-        <v>109.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X36" t="n">
-        <v>63.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y36" t="n">
-        <v>63.68269577730436</v>
+        <v>58.71346549096932</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>37.8319801819373</v>
+        <v>32.86274989560226</v>
       </c>
       <c r="C37" t="n">
-        <v>25.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D37" t="n">
-        <v>6.615473018212356</v>
+        <v>10.33589095610849</v>
       </c>
       <c r="E37" t="n">
-        <v>4.433962646569171</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>3.421048022931245</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>25.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H37" t="n">
-        <v>20.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I37" t="n">
-        <v>13.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>35.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S37" t="n">
-        <v>82.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T37" t="n">
-        <v>85.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U37" t="n">
-        <v>144.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V37" t="n">
-        <v>110.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W37" t="n">
-        <v>144.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X37" t="n">
-        <v>83.70965538903715</v>
+        <v>78.74042510270212</v>
       </c>
       <c r="Y37" t="n">
-        <v>76.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>240.7338416634806</v>
+        <v>235.7646113771455</v>
       </c>
       <c r="C38" t="n">
-        <v>223.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D38" t="n">
-        <v>212.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E38" t="n">
-        <v>239.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F38" t="n">
-        <v>264.8760457417114</v>
+        <v>259.9068154553764</v>
       </c>
       <c r="G38" t="n">
-        <v>273.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H38" t="n">
-        <v>197.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I38" t="n">
-        <v>68.47588957040591</v>
+        <v>63.50665928407087</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.869117941149682</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S38" t="n">
-        <v>67.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T38" t="n">
-        <v>81.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U38" t="n">
-        <v>109.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V38" t="n">
-        <v>185.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W38" t="n">
-        <v>207.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X38" t="n">
-        <v>227.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y38" t="n">
-        <v>244.2379386560536</v>
+        <v>240.416093373995</v>
       </c>
     </row>
     <row r="39">
@@ -25427,19 +25427,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C39" t="n">
-        <v>30.70849898831574</v>
+        <v>34.61234893643037</v>
       </c>
       <c r="D39" t="n">
-        <v>5.445065564638753</v>
+        <v>0.4758352783037125</v>
       </c>
       <c r="E39" t="n">
-        <v>15.64508045540094</v>
+        <v>10.6758501690659</v>
       </c>
       <c r="F39" t="n">
-        <v>3.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>29.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T39" t="n">
-        <v>58.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U39" t="n">
-        <v>83.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V39" t="n">
-        <v>90.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W39" t="n">
-        <v>109.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X39" t="n">
-        <v>63.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y39" t="n">
-        <v>63.68269577730436</v>
+        <v>58.71346549096932</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>37.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C40" t="n">
-        <v>25.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D40" t="n">
-        <v>6.615473018212356</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E40" t="n">
-        <v>4.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F40" t="n">
-        <v>3.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G40" t="n">
-        <v>25.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H40" t="n">
-        <v>20.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I40" t="n">
-        <v>13.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>35.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S40" t="n">
-        <v>82.01659803697225</v>
+        <v>78.19475275491365</v>
       </c>
       <c r="T40" t="n">
-        <v>85.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U40" t="n">
-        <v>144.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V40" t="n">
-        <v>110.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W40" t="n">
-        <v>144.522998336591</v>
+        <v>139.553768050256</v>
       </c>
       <c r="X40" t="n">
-        <v>83.70965538903715</v>
+        <v>78.74042510270212</v>
       </c>
       <c r="Y40" t="n">
-        <v>76.58465335209479</v>
+        <v>71.61542306575976</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>248.7338416634806</v>
+        <v>253.3770665896247</v>
       </c>
       <c r="C41" t="n">
-        <v>231.2728917710076</v>
+        <v>235.9161166971517</v>
       </c>
       <c r="D41" t="n">
-        <v>220.683041620683</v>
+        <v>225.3262665468271</v>
       </c>
       <c r="E41" t="n">
-        <v>247.9303700722618</v>
+        <v>252.573594998406</v>
       </c>
       <c r="F41" t="n">
-        <v>272.8760457417114</v>
+        <v>277.5192706678556</v>
       </c>
       <c r="G41" t="n">
-        <v>281.302737515135</v>
+        <v>285.9459624412792</v>
       </c>
       <c r="H41" t="n">
-        <v>205.4748021157671</v>
+        <v>210.1180270419113</v>
       </c>
       <c r="I41" t="n">
-        <v>76.47588957040591</v>
+        <v>81.11911449655008</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>15.86911794114968</v>
+        <v>12.03401474844588</v>
       </c>
       <c r="S41" t="n">
-        <v>75.02006958624534</v>
+        <v>79.66329451238951</v>
       </c>
       <c r="T41" t="n">
-        <v>89.09584956413136</v>
+        <v>93.73907449027553</v>
       </c>
       <c r="U41" t="n">
-        <v>117.3456529078365</v>
+        <v>121.9888778339807</v>
       </c>
       <c r="V41" t="n">
-        <v>193.7522584701349</v>
+        <v>188.7697702731547</v>
       </c>
       <c r="W41" t="n">
-        <v>215.240968717413</v>
+        <v>210.2584805204328</v>
       </c>
       <c r="X41" t="n">
-        <v>235.731100678469</v>
+        <v>230.7486124814888</v>
       </c>
       <c r="Y41" t="n">
-        <v>252.2379386560536</v>
+        <v>256.8811635821978</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32.53318364986734</v>
+        <v>28.69808045716353</v>
       </c>
       <c r="C42" t="n">
-        <v>38.70849898831574</v>
+        <v>43.35172391445991</v>
       </c>
       <c r="D42" t="n">
-        <v>13.44506556463875</v>
+        <v>18.08829049078292</v>
       </c>
       <c r="E42" t="n">
-        <v>23.64508045540094</v>
+        <v>28.28830538154511</v>
       </c>
       <c r="F42" t="n">
-        <v>11.06921239338388</v>
+        <v>15.71243731952805</v>
       </c>
       <c r="G42" t="n">
-        <v>3.343517163210635</v>
+        <v>7.986742089354806</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>37.68317110383782</v>
+        <v>42.32639602998199</v>
       </c>
       <c r="T42" t="n">
-        <v>66.1647286948216</v>
+        <v>61.18224049784137</v>
       </c>
       <c r="U42" t="n">
-        <v>91.94138208097482</v>
+        <v>96.58460700711899</v>
       </c>
       <c r="V42" t="n">
-        <v>98.80058714942527</v>
+        <v>103.4438120755694</v>
       </c>
       <c r="W42" t="n">
-        <v>117.6949831609196</v>
+        <v>112.7124949639394</v>
       </c>
       <c r="X42" t="n">
-        <v>71.77298520347748</v>
+        <v>76.41621012962165</v>
       </c>
       <c r="Y42" t="n">
-        <v>71.68269577730436</v>
+        <v>66.70020758032413</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>45.8319801819373</v>
+        <v>50.47520510808147</v>
       </c>
       <c r="C43" t="n">
-        <v>33.24682109862783</v>
+        <v>37.890046024772</v>
       </c>
       <c r="D43" t="n">
-        <v>14.61547301821236</v>
+        <v>9.632984821232121</v>
       </c>
       <c r="E43" t="n">
-        <v>12.43396264656917</v>
+        <v>7.451474449588936</v>
       </c>
       <c r="F43" t="n">
-        <v>11.42104802293125</v>
+        <v>16.06427294907542</v>
       </c>
       <c r="G43" t="n">
-        <v>33.99097935845876</v>
+        <v>38.63420428460293</v>
       </c>
       <c r="H43" t="n">
-        <v>28.22717250743958</v>
+        <v>32.87039743358375</v>
       </c>
       <c r="I43" t="n">
-        <v>21.45047492725828</v>
+        <v>17.61537173455448</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>43.29339137716948</v>
+        <v>47.93661630331366</v>
       </c>
       <c r="S43" t="n">
-        <v>90.01659803697225</v>
+        <v>85.03410983999203</v>
       </c>
       <c r="T43" t="n">
-        <v>93.94558942828149</v>
+        <v>98.58881435442566</v>
       </c>
       <c r="U43" t="n">
-        <v>152.3190293564909</v>
+        <v>156.9622542826351</v>
       </c>
       <c r="V43" t="n">
-        <v>118.137643323828</v>
+        <v>122.7808682499722</v>
       </c>
       <c r="W43" t="n">
-        <v>152.522998336591</v>
+        <v>157.1662232627352</v>
       </c>
       <c r="X43" t="n">
-        <v>91.70965538903715</v>
+        <v>96.35288031518132</v>
       </c>
       <c r="Y43" t="n">
-        <v>84.58465335209479</v>
+        <v>89.22787827823896</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>318445.2791038891</v>
+        <v>316294.6845549099</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>480477.0170674367</v>
+        <v>481184.5875300774</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>480477.0170674367</v>
+        <v>481184.5875300774</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>480477.0170674367</v>
+        <v>488602.7182850761</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>480477.0170674368</v>
+        <v>488602.7182850761</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>470576.8824194716</v>
+        <v>480796.6586744089</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>573264.2584535236</v>
+        <v>572107.7554535451</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>573264.2584535236</v>
+        <v>572107.755453545</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>573264.2584535236</v>
+        <v>572107.7554535451</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>573264.2584535236</v>
+        <v>572107.7554535448</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>558412.2380949615</v>
+        <v>557112.806915623</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>737348.7048453346</v>
+        <v>737348.7048453349</v>
       </c>
       <c r="C2" t="n">
-        <v>737348.7048453343</v>
+        <v>737348.7048453349</v>
       </c>
       <c r="D2" t="n">
         <v>737348.7048453344</v>
       </c>
       <c r="E2" t="n">
-        <v>223345.9837825864</v>
+        <v>221068.8836719024</v>
       </c>
       <c r="F2" t="n">
-        <v>394909.0004498719</v>
+        <v>395658.1927044325</v>
       </c>
       <c r="G2" t="n">
-        <v>394909.0004498719</v>
+        <v>395658.1927044325</v>
       </c>
       <c r="H2" t="n">
-        <v>394909.000449872</v>
+        <v>400566.7011323849</v>
       </c>
       <c r="I2" t="n">
-        <v>394909.0004498719</v>
+        <v>400566.7011323852</v>
       </c>
       <c r="J2" t="n">
-        <v>384426.5049402619</v>
+        <v>392301.4615446198</v>
       </c>
       <c r="K2" t="n">
-        <v>493154.31485867</v>
+        <v>488983.7993107627</v>
       </c>
       <c r="L2" t="n">
-        <v>493154.3148586699</v>
+        <v>488983.7993107635</v>
       </c>
       <c r="M2" t="n">
-        <v>493154.3148586699</v>
+        <v>488983.7993107635</v>
       </c>
       <c r="N2" t="n">
-        <v>493154.3148586698</v>
+        <v>488983.7993107635</v>
       </c>
       <c r="O2" t="n">
-        <v>477428.6462437221</v>
+        <v>473106.7949764938</v>
       </c>
       <c r="P2" t="n">
         <v>193513.3299566035</v>
@@ -26322,25 +26322,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10400</v>
+        <v>9559.431483690014</v>
       </c>
       <c r="F3" t="n">
-        <v>64000</v>
+        <v>65127.91260964821</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2597.104032037073</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6400</v>
+        <v>6389.393671483856</v>
       </c>
       <c r="K3" t="n">
-        <v>107200</v>
+        <v>103485.4200590847</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="C4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="D4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="E4" t="n">
-        <v>126426.8461766621</v>
+        <v>124455.3967726702</v>
       </c>
       <c r="F4" t="n">
-        <v>235229.6476198197</v>
+        <v>235177.4293748555</v>
       </c>
       <c r="G4" t="n">
-        <v>235229.6476198197</v>
+        <v>235177.4293748556</v>
       </c>
       <c r="H4" t="n">
-        <v>235229.6476198197</v>
+        <v>237954.4457466482</v>
       </c>
       <c r="I4" t="n">
-        <v>235229.6476198197</v>
+        <v>237954.4457466482</v>
       </c>
       <c r="J4" t="n">
-        <v>228581.7995012901</v>
+        <v>232712.7494928938</v>
       </c>
       <c r="K4" t="n">
-        <v>297535.4151680265</v>
+        <v>294027.2996994237</v>
       </c>
       <c r="L4" t="n">
-        <v>297535.4151680265</v>
+        <v>294027.2996994237</v>
       </c>
       <c r="M4" t="n">
-        <v>297535.4151680265</v>
+        <v>294027.2996994237</v>
       </c>
       <c r="N4" t="n">
-        <v>297535.4151680265</v>
+        <v>294027.2996994237</v>
       </c>
       <c r="O4" t="n">
-        <v>287562.4219605729</v>
+        <v>283958.3315520296</v>
       </c>
       <c r="P4" t="n">
-        <v>107507.4055314464</v>
+        <v>106980.0603174001</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1092.897</v>
+        <v>1004.56480675292</v>
       </c>
       <c r="F5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7818.417</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7818.417</v>
+        <v>8433.856271114528</v>
       </c>
       <c r="I5" t="n">
-        <v>7818.417</v>
+        <v>8433.856271114528</v>
       </c>
       <c r="J5" t="n">
-        <v>7398.072</v>
+        <v>8100.728885071578</v>
       </c>
       <c r="K5" t="n">
-        <v>11937.798</v>
+        <v>12131.57550227992</v>
       </c>
       <c r="L5" t="n">
-        <v>11937.798</v>
+        <v>12131.57550227992</v>
       </c>
       <c r="M5" t="n">
-        <v>11937.798</v>
+        <v>12131.57550227992</v>
       </c>
       <c r="N5" t="n">
-        <v>11937.798</v>
+        <v>12131.57550227992</v>
       </c>
       <c r="O5" t="n">
-        <v>11265.246</v>
+        <v>11460.13808156995</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>251321.1142963695</v>
+        <v>251848.4595104161</v>
       </c>
       <c r="C6" t="n">
-        <v>251321.1142963691</v>
+        <v>251848.4595104161</v>
       </c>
       <c r="D6" t="n">
-        <v>251321.1142963692</v>
+        <v>251848.4595104156</v>
       </c>
       <c r="E6" t="n">
-        <v>85426.24060592428</v>
+        <v>86049.49060878922</v>
       </c>
       <c r="F6" t="n">
-        <v>87860.93583005214</v>
+        <v>87504.23780670017</v>
       </c>
       <c r="G6" t="n">
-        <v>151860.9358300522</v>
+        <v>152632.1504163484</v>
       </c>
       <c r="H6" t="n">
-        <v>151860.9358300523</v>
+        <v>151581.295082585</v>
       </c>
       <c r="I6" t="n">
-        <v>151860.9358300522</v>
+        <v>154178.3991146224</v>
       </c>
       <c r="J6" t="n">
-        <v>142046.6334389719</v>
+        <v>145098.5894951706</v>
       </c>
       <c r="K6" t="n">
-        <v>76481.10169064354</v>
+        <v>79339.50404997444</v>
       </c>
       <c r="L6" t="n">
-        <v>183681.1016906435</v>
+        <v>182824.9241090599</v>
       </c>
       <c r="M6" t="n">
-        <v>183681.1016906434</v>
+        <v>182824.9241090599</v>
       </c>
       <c r="N6" t="n">
-        <v>183681.1016906433</v>
+        <v>182824.9241090599</v>
       </c>
       <c r="O6" t="n">
-        <v>178600.9782831492</v>
+        <v>177688.3253428942</v>
       </c>
       <c r="P6" t="n">
-        <v>86005.92442515712</v>
+        <v>86533.26963920347</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L2" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M2" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="N2" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="O2" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,40 +26849,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>7.98674208935482</v>
       </c>
       <c r="K2" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,13 +26947,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -26962,31 +26962,31 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
-        <v>80</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>7.98674208935482</v>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
     </row>
     <row r="3">
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
     </row>
   </sheetData>
@@ -28012,28 +28012,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="13">
@@ -28170,34 +28170,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,31 +28407,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -28455,28 +28455,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,31 +28644,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K19" t="n">
         <v>22.26949182588285</v>
@@ -28692,28 +28692,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,31 +28881,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
         <v>22.26949182588285</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,31 +29118,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
-        <v>93.00000000000172</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
         <v>22.26949182588285</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>93</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,28 +29276,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29403,28 +29403,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>88</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y29" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="30">
@@ -29513,19 +29513,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
@@ -29564,25 +29564,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y30" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y31" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y32" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="33">
@@ -29750,19 +29750,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
@@ -29801,25 +29801,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y33" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y34" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y35" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="36">
@@ -29987,19 +29987,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y36" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y37" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y38" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="39">
@@ -30224,19 +30224,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y39" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y40" t="n">
-        <v>142</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="C41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="D41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="E41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="F41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="G41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="H41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="I41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="S41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="T41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="U41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="V41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="W41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="X41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="Y41" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="C42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="D42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="E42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="F42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="G42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30512,25 +30512,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="T42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="U42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="V42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="W42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="X42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="Y42" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="C43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="D43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="E43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="F43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="G43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="H43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="I43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="S43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="T43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="U43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="V43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="W43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="X43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
       <c r="Y43" t="n">
-        <v>134</v>
+        <v>129.3567750738558</v>
       </c>
     </row>
     <row r="44">
@@ -36042,16 +36042,16 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,16 +36115,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -36133,7 +36133,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36197,16 +36197,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -36279,16 +36279,16 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36355,16 +36355,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -36434,16 +36434,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -36513,16 +36513,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36595,16 +36595,16 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36671,16 +36671,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -36747,16 +36747,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36826,7 +36826,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -36838,13 +36838,13 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36908,16 +36908,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -36987,16 +36987,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37063,16 +37063,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -37145,16 +37145,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -37221,19 +37221,19 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37309,16 +37309,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37382,16 +37382,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -37458,16 +37458,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -37546,16 +37546,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37619,16 +37619,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -37701,16 +37701,16 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,22 +37774,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37856,16 +37856,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>9.625713123124406</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>9.236795421179986</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
